--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.141.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.141.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.141" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.141" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.141.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.141.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0141.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0141.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -887,7 +887,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.141.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.141.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.141" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.141" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -603,18 +603,18 @@
           <t>L16: suspicious token(s): own1 (letter/digit mix) :: for his own1</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” your orator and the said C. D. en-</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: which was â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]134</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]134</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 134</t>
@@ -622,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: 3</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]134</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -661,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -678,14 +678,10 @@
           <t>L42: suspicious token(s): 4c (letter/digit mix) :: certain estate for the life, 4c., as the case may be)* of</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” part of, the</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” ---------years, (or for an indefinite time) ; that the</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: which was €</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -695,7 +691,11 @@
           <t>L43: isolated marker/symbol line :: 3</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L108: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
@@ -703,7 +703,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • If either party fills a representative character, say that the said</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -737,14 +741,10 @@
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (Pray subpa Ã¦ na).</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L121: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ If either party fills a representative character, say that the said</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • If either party fills a representative character, say that the said</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -778,12 +778,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -796,16 +796,8 @@
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -â€”, co-</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L127: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: , and the said â€”â€”</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -855,16 +847,8 @@
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” under cer-</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L129: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”is his executor, or administrator, or heir-at-law.</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
@@ -910,11 +894,7 @@
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” your orator and the said C. D. en-</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -957,11 +937,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” part of, the</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
@@ -970,7 +946,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” ---------years, (or for an indefinite time) ; that the</t>
+          <t>L114: punctuation artifact: double/multiple hyphen :: — ---------years, (or for an indefinite time) ; that the</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1004,11 +980,7 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (Pray subpa Ã¦ na).</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
@@ -1037,12 +1009,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1051,11 +1023,7 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -â€”, co-</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
@@ -1085,7 +1053,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1094,11 +1062,7 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L143: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” under cer-</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
@@ -1128,7 +1092,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1137,11 +1101,7 @@
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L164: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: , and the said â€”</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
@@ -1180,11 +1140,7 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L170: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: , and the said â€”</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
@@ -1214,7 +1170,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
